--- a/Assets/LingBoCanteen/Datatables/Excel/Music.xlsx
+++ b/Assets/LingBoCanteen/Datatables/Excel/Music.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\GoldenDolphin\Assets\LingBoCanteen\1_Datatables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\project\GoldenDolphin\GoldenDolphin\GoldenDolphinGame\Assets\LingBoCanteen\Datatables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99844133-B6BC-4E2E-B833-5D72B4D56CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF71872-BCE1-415B-B76F-D632E389EB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>#</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,6 +61,54 @@
   <si>
     <t>背景音乐配置表</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主菜单封面循环 BGM</t>
+  </si>
+  <si>
+    <t>bgm_main_menu</t>
+  </si>
+  <si>
+    <t>人间区域白天经营 BGM</t>
+  </si>
+  <si>
+    <t>bgm_human_day</t>
+  </si>
+  <si>
+    <t>天堂区域经营 BGM</t>
+  </si>
+  <si>
+    <t>bgm_heaven</t>
+  </si>
+  <si>
+    <t>地狱区域经营 BGM</t>
+  </si>
+  <si>
+    <t>bgm_hell</t>
+  </si>
+  <si>
+    <t>傍晚超市采购 BGM</t>
+  </si>
+  <si>
+    <t>bgm_supermarket</t>
+  </si>
+  <si>
+    <t>夜晚结算剧情 BGM</t>
+  </si>
+  <si>
+    <t>bgm_night_settle</t>
+  </si>
+  <si>
+    <t>紧张倒计时危急 BGM</t>
+  </si>
+  <si>
+    <t>bgm_tension</t>
+  </si>
+  <si>
+    <t>普通结局片尾曲</t>
+  </si>
+  <si>
+    <t>bgm_end_normal</t>
   </si>
 </sst>
 </file>
@@ -91,7 +139,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -99,14 +147,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -388,14 +454,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.06640625" customWidth="1"/>
+    <col min="2" max="2" width="14.08203125" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -406,7 +473,7 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -419,7 +486,7 @@
       </c>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -432,7 +499,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -447,23 +514,97 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="2">
+        <v>30000</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="2">
+        <v>30001</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="2">
+        <v>30002</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8" s="2">
+        <v>30003</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B9" s="2">
+        <v>30004</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="2">
+        <v>30005</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="42.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="2">
+        <v>30006</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="2">
+        <v>30007</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
